--- a/AtchisonRegime/Outputs/USA/USA500_Industrials/df_regSummary_USA500_Industrials.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Industrials/df_regSummary_USA500_Industrials.xlsx
@@ -530,13 +530,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.939399161532498</v>
+        <v>1.88979785231731</v>
       </c>
       <c r="H2" t="n">
-        <v>4.183119601461454</v>
+        <v>4.16788365469603</v>
       </c>
       <c r="I2" t="n">
         <v>-5.93862228897025</v>
@@ -545,16 +545,16 @@
         <v>13.5073547998131</v>
       </c>
       <c r="K2" t="n">
-        <v>38.75</v>
+        <v>39.1304347826087</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2855275258317235</v>
+        <v>0.2823707548130373</v>
       </c>
       <c r="O2" t="n">
         <v>-0.006648237576164506</v>
@@ -603,7 +603,7 @@
         <v>11.9900891508605</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L3" t="n">
         <v>5</v>
@@ -661,7 +661,7 @@
         <v>7.456744942287171</v>
       </c>
       <c r="K4" t="n">
-        <v>20</v>
+        <v>19.87577639751553</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
@@ -719,7 +719,7 @@
         <v>14.5269451461826</v>
       </c>
       <c r="K5" t="n">
-        <v>21.25</v>
+        <v>21.11801242236025</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
